--- a/Master/6841r00/6841r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/6841r00/6841r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -854,222 +854,282 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>1.117</v>
+        <v>3.225</v>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.4752</v>
+        <v>3.3988</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>-0.1932</v>
+        <v>-1.4711</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0309</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>5.118</v>
+        <v>1.227</v>
       </c>
       <c r="B22" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>3.5925</v>
+        <v>3.4013</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-0.1394</v>
+        <v>-1.8601</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0275</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>4.119</v>
+        <v>2.226</v>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3.6944</v>
+        <v>3.4013</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>-0.3507</v>
+        <v>-1.6564</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0236</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>3.12</v>
+        <v>1.117</v>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.7781</v>
+        <v>3.4752</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.1932</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0179</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>2.121</v>
+        <v>5.118</v>
       </c>
       <c r="B25" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>3.8439</v>
+        <v>3.5925</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>-0.7902</v>
+        <v>-0.1394</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>0.0147</v>
+        <v>0.0275</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>1.122</v>
+        <v>4.119</v>
       </c>
       <c r="B26" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.8935</v>
+        <v>3.6944</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>-1.018</v>
+        <v>-0.3507</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>0.0101</v>
+        <v>0.0236</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>5.123</v>
+        <v>3.12</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.9214</v>
+        <v>3.7781</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>-0.9833</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.0044</v>
+        <v>0.0179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>4.124</v>
+        <v>2.121</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.9319</v>
+        <v>3.8439</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>-1.1728</v>
+        <v>-0.7902</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0147</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>2.126</v>
+        <v>1.122</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>3.9357</v>
+        <v>3.8935</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>-1.6046</v>
+        <v>-1.018</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
+        <v>5.123</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>3.9214</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>-0.9833</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0.0044</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n">
+        <v>4.124</v>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>3.9319</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>-1.1728</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n">
+        <v>2.126</v>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>3.9357</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>-1.6046</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
         <v>3.125</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B33" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="7" t="n">
+      <c r="C33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="7" t="n">
         <v>3.9359</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E33" s="7" t="n">
         <v>-1.3949</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F33" s="7" t="n">
         <v>0.0001</v>
       </c>
     </row>
-    <row r="32">
-      <c r="E32" s="8" t="inlineStr">
+    <row r="35">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F32" s="9" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="E33" s="8" t="inlineStr">
+      <c r="F35" s="9" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F33" s="10" t="n">
-        <v>0.9737</v>
+      <c r="F36" s="10" t="n">
+        <v>0.9745</v>
       </c>
     </row>
   </sheetData>
